--- a/PO_TBD_20260619.xlsx
+++ b/PO_TBD_20260619.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -633,13 +633,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>42.4</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>212</v>
+        <v>254.4</v>
       </c>
     </row>
     <row r="11">
@@ -1622,16 +1622,16 @@
         </is>
       </c>
       <c r="E41" s="8" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="G41" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>2.66</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="42">
@@ -1654,16 +1654,16 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1.81</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>362</v>
+        <v>380.1</v>
       </c>
     </row>
     <row r="43">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
+          <t>INJ ZYCORT (HYDROCORTISONE) 100MG VIAL SM PHARMA</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1714,20 +1714,20 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>0.58</v>
+        <v>5.4</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>52.78</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="45">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
+          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -1746,20 +1746,20 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E45" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>3.7</v>
+        <v>0.58</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>74</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="46">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
+          <t>SYR BUCANIL (TERBUTALINE SULPHATE 1.5MG/5ML) 100ML Y.S.P.</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -1778,20 +1778,20 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
         <v>10</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>1.62</v>
+        <v>3.7</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>63.18</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
+          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -1817,13 +1817,13 @@
         <v>10</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>30.6</v>
+        <v>63.18</v>
       </c>
     </row>
     <row r="48">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
+          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -1842,20 +1842,20 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>39.84</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="49">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
+          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -1874,20 +1874,20 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>33.92</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="50">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>INJ MALON ( METOCLOPRAMIDE ) 10MG/2ML DUOPHARMA</t>
+          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -1906,20 +1906,20 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>2.14</v>
+        <v>1.06</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>10.7</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="51">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
+          <t>INJ MALON ( METOCLOPRAMIDE ) 10MG/2ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -1938,20 +1938,20 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E51" s="8" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>0.68</v>
+        <v>2.14</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>54.4</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="52">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
+          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>1.44</v>
+        <v>0.68</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>28.8</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="53">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
+          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2002,20 +2002,20 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E53" s="8" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>103.67</v>
+        <v>1.44</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>1347.71</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="54">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>NASAL DROPS ILIADIN  0.025% DECONGESTANT (1-6 YEARS) P&amp;G</t>
+          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -2034,20 +2034,20 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>2</v>
+        <v>11.5</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>10.94</v>
+        <v>103.67</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>87.52</v>
+        <v>1347.71</v>
       </c>
     </row>
     <row r="55">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>TAB PLAVIX (CLOPIDOGREL) 75MG SANOFI</t>
+          <t>NASAL DROPS ILIADIN  0.025% DECONGESTANT (1-6 YEARS) P&amp;G</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -2066,20 +2066,20 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E55" s="8" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>6.94</v>
+        <v>10.94</v>
       </c>
       <c r="H55" s="10" t="n">
-        <v>430.28</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="56">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>TAB YASMIN (DROSPIRENONE 3MG/ ETHINYLESTRADIOL 0.03MG) BAYER</t>
+          <t>TAB PLAVIX (CLOPIDOGREL) 75MG SANOFI</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -2102,16 +2102,16 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>2.33</v>
+        <v>6.94</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>48.93</v>
+        <v>430.28</v>
       </c>
     </row>
     <row r="57">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
+          <t>TAB YASMIN (DROSPIRENONE 3MG/ ETHINYLESTRADIOL 0.03MG) BAYER</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -2130,20 +2130,20 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E57" s="8" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>5.5</v>
+        <v>2.33</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>38.5</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="58">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>TAB NORMATEN (ATENOLOL) 100MG XEPA</t>
+          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -2162,20 +2162,20 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>0.52</v>
+        <v>5.5</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>12.48</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="59">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>TAB COAPROVEL (IRBESARTAN/ HYDROCHOLOTHIAZIDE) 150MG/12.5MG SANOFI</t>
+          <t>TAB NORMATEN (ATENOLOL) 100MG XEPA</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -2204,10 +2204,10 @@
         <v>24</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>1.82</v>
+        <v>0.52</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>43.68</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="60">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>TAB NOVOMIN (DIMENHYDRINATE) 50MG XEPA</t>
+          <t>TAB COAPROVEL (IRBESARTAN/ HYDROCHOLOTHIAZIDE) 150MG/12.5MG SANOFI</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2230,16 +2230,16 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.28</v>
+        <v>1.82</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>19.6</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="61">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
+          <t>TAB NOVOMIN (DIMENHYDRINATE) 50MG XEPA</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -2258,20 +2258,20 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E61" s="8" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>9.65</v>
+        <v>0.28</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>38.6</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="62">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>EFFERVESCENT ACETYLCYSTIENE (N-ACETYLCYSTIENE) 600MG 2'S SANDOZ</t>
+          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2290,20 +2290,20 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>STRIP</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>2.17</v>
+        <v>9.65</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>36.89</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="63">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>TAB ROWATINEX ( PINENE 31MG, CAMPHENE 31MG, CINEOL 3MG, FENCHONE 4MG, BORNEOL 10MG, ANETHOL 4MG ) DCH AURIGA</t>
+          <t>EFFERVESCENT ACETYLCYSTIENE (N-ACETYLCYSTIENE) 600MG 2'S SANDOZ</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>STRIP</t>
         </is>
       </c>
       <c r="E63" s="8" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>0.66</v>
+        <v>2.17</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>132</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="64">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>CREAM CLODERM (CLOBETASOL 0.05% W/W) 15G HOE</t>
+          <t>TAB ROWATINEX ( PINENE 31MG, CAMPHENE 31MG, CINEOL 3MG, FENCHONE 4MG, BORNEOL 10MG, ANETHOL 4MG ) DCH AURIGA</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2354,20 +2354,20 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>10.5</v>
+        <v>0.66</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>73.5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>IVD N/S 0.9% 500ML B. BRAUN</t>
+          <t>CREAM CLODERM (CLOBETASOL 0.05% W/W) 15G HOE</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -2386,20 +2386,20 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E65" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F65" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="G65" s="10" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>11.4</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="66">
@@ -2408,30 +2408,30 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>ALLERGOCROM  (SODIUM CROMOGLYCATE ) 2% EYE DROPS 10ML PHARMAFORTE URSAPHARM</t>
+          <t>IVD N/S 0.9% 500ML B. BRAUN</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>PHARMAFORTE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F66" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="G66" s="7" t="n">
-        <v>16.5</v>
+        <v>3.8</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>115.5</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="67">
@@ -2440,30 +2440,30 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>AQUA CREAM (PARAFFIN, WHITE SOFT CREAM) 500GM DUOPHARMA</t>
+          <t>ALLERGOCROM  (SODIUM CROMOGLYCATE ) 2% EYE DROPS 10ML PHARMAFORTE URSAPHARM</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PHARMAFORTE</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>JAR</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E67" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>34</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="68">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>BABY DROPS 30ML( VITAMIN A 1333IU, VITAMIN D3 438IU, VITAMIN E 6.57IU, VITAMIN B1 218MCG, VITAMIN B2 336MCG, VITAMIN B6 108MCG, NICOTINAMIDE 2.15MG, TAURINE 15MG, L-LYSINE 20MG PER ML) APPETON</t>
+          <t>AQUA CREAM (PARAFFIN, WHITE SOFT CREAM) 500GM DUOPHARMA</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -2482,20 +2482,20 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>JAR</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>43.29</v>
+        <v>17</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>389.61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>INJECSOL MgSO4 (Magnesium Sulfate 50% W/v 2.465G) 5ML VIAL AIN MEDICARE</t>
+          <t>BABY DROPS 30ML( VITAMIN A 1333IU, VITAMIN D3 438IU, VITAMIN E 6.57IU, VITAMIN B1 218MCG, VITAMIN B2 336MCG, VITAMIN B6 108MCG, NICOTINAMIDE 2.15MG, TAURINE 15MG, L-LYSINE 20MG PER ML) APPETON</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -2514,20 +2514,20 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>20</v>
+        <v>43.29</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>20</v>
+        <v>389.61</v>
       </c>
     </row>
     <row r="70">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>INJ AMINOPHYLLIN 250MG/10ML FRESENIUS</t>
+          <t>INJECSOL MgSO4 (Magnesium Sulfate 50% W/v 2.465G) 5ML VIAL AIN MEDICARE</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -2550,16 +2550,16 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>8.5</v>
+        <v>20</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>INJ ACIPAN (ATROPINE SULPHATE) 1MG/ML 1ML DUOPHARMA</t>
+          <t>INJ AMINOPHYLLIN 250MG/10ML FRESENIUS</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -2588,10 +2588,10 @@
         <v>8</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>2.32</v>
+        <v>8.5</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>18.56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>A SCABS ( PERMETHRIN 5% ) LOTION 30ML HOE</t>
+          <t>INJ ACIPAN (ATROPINE SULPHATE) 1MG/ML 1ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -2610,20 +2610,20 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>11.6</v>
+        <v>2.32</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>104.4</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="73">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>T3 MYCIN LOTION (CLINDAMYCIN PHOSPHATE 1%) 30ML HOE</t>
+          <t>A SCABS ( PERMETHRIN 5% ) LOTION 30ML HOE</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E73" s="8" t="n">
@@ -2652,10 +2652,10 @@
         <v>9</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>27</v>
+        <v>11.6</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>243</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="74">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>KAOLIN-PECTIN (PECTIN 25MG/5ML, LIGHT KAOLIN 1G/5ML) 120ML DYNA</t>
+          <t>T3 MYCIN LOTION (CLINDAMYCIN PHOSPHATE 1%) 30ML HOE</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -2674,20 +2674,20 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>4.64</v>
+        <v>27</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>32.48</v>
+        <v>243</v>
       </c>
     </row>
     <row r="75">
@@ -2696,30 +2696,30 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>SUPP DIMENHYDRINATE 50MG DRIMINATE Y.S.P</t>
+          <t>KAOLIN-PECTIN (PECTIN 25MG/5ML, LIGHT KAOLIN 1G/5ML) 120ML DYNA</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>DRIMINATE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E75" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>1.29</v>
+        <v>4.64</v>
       </c>
       <c r="H75" s="10" t="n">
-        <v>7.74</v>
+        <v>32.48</v>
       </c>
     </row>
     <row r="76">
@@ -2728,30 +2728,30 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>NITROSOL SUBLINGUAL AEROSOL SPRAY 400mcg/PER SPRAY VITAMODE</t>
+          <t>SUPP DIMENHYDRINATE 50MG DRIMINATE Y.S.P</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DRIMINATE</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>SPRAY</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>55</v>
+        <v>1.29</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>110</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="77">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>INJ TYPHIM IV ( TYPHOID VACCINE ) SANOFI</t>
+          <t>NITROSOL SUBLINGUAL AEROSOL SPRAY 400mcg/PER SPRAY VITAMODE</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -2770,20 +2770,20 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>SPRAY</t>
         </is>
       </c>
       <c r="E77" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F77" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="G77" s="10" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H77" s="10" t="n">
-        <v>177</v>
+        <v>110</v>
       </c>
     </row>
     <row r="78">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>GENGIGEL SPRAY ( SODIUM HYALURONATE 0.01% ) 20ML PHARMANIAGA</t>
+          <t>INJ TYPHIM IV ( TYPHOID VACCINE ) SANOFI</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
@@ -2812,10 +2812,10 @@
         <v>3</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>105</v>
+        <v>177</v>
       </c>
     </row>
     <row r="79">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>PREVENAR 13 (PNEUMOCOCCAL POLYSACCHARIDE CONJUGATE 13-VALENT) PFIZER</t>
+          <t>GENGIGEL SPRAY ( SODIUM HYALURONATE 0.01% ) 20ML PHARMANIAGA</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -2834,20 +2834,20 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E79" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>219</v>
+        <v>35</v>
       </c>
       <c r="H79" s="10" t="n">
-        <v>876</v>
+        <v>105</v>
       </c>
     </row>
     <row r="80">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>SYR DESTACURE ( DESLORATIDINE 2.5MG/5ML ) 60ML HEALOL</t>
+          <t>PREVENAR 13 (PNEUMOCOCCAL POLYSACCHARIDE CONJUGATE 13-VALENT) PFIZER</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -2866,20 +2866,20 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>8.73</v>
+        <v>219</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>78.56999999999999</v>
+        <v>876</v>
       </c>
     </row>
     <row r="81">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>MONITAZONE (MOMETASONE FUROATE) 50MCG/ACTUATION NASAL SPRAY 140MD SHAMCHUNDANG PHARM</t>
+          <t>SYR DESTACURE ( DESLORATIDINE 2.5MG/5ML ) 60ML HEALOL</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -2902,16 +2902,16 @@
         </is>
       </c>
       <c r="E81" s="8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>50</v>
+        <v>8.73</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>150</v>
+        <v>78.56999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+          <t>MONITAZONE (MOMETASONE FUROATE) 50MCG/ACTUATION NASAL SPRAY 140MD SHAMCHUNDANG PHARM</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -2930,20 +2930,20 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>7.4</v>
+        <v>50</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>59.2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="83">
@@ -2952,58 +2952,90 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
+          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>AMPULE</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H83" s="10" t="n">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
           <t>TAB AUROXETIL 500 (Cefuroxime 500 Mg) Aurobindo Pharma</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>TABLET</t>
         </is>
       </c>
-      <c r="E83" s="8" t="n">
+      <c r="E84" s="5" t="n">
         <v>410</v>
       </c>
-      <c r="F83" s="8" t="n">
+      <c r="F84" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="G83" s="10" t="n">
+      <c r="G84" s="7" t="n">
         <v>1.44</v>
       </c>
-      <c r="H83" s="10" t="n">
+      <c r="H84" s="7" t="n">
         <v>129.6</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="11" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="H84" s="12" t="n">
-        <v>9116.57</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Total line items: 74</t>
-        </is>
+      <c r="H85" s="12" t="n">
+        <v>9189.83</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-19 00:55</t>
+          <t>Total line items: 75</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="13" t="inlineStr">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Generated: 2026-06-19 08:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
         <is>
           <t>Note: Unit costs are from latest purchase price. Verify with supplier before confirming order.</t>
         </is>
@@ -3011,8 +3043,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A84:G84"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A85:G85"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
